--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UROS DE RIVAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UROS DE RIVAS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9527</v>
+        <v>6.5136</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1435</v>
+        <v>4.6285</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8092</v>
+        <v>1.885</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0838</v>
+        <v>5.496499999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8379</v>
+        <v>1.1762</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7541</v>
+        <v>4.3202</v>
       </c>
       <c r="J2" t="n">
-        <v>2.916</v>
+        <v>7.389199999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7826</v>
+        <v>1.9812</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8665000000000003</v>
+        <v>5.4079</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-1.8927</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05530000000000002</v>
+        <v>-0.8049999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8875</v>
+        <v>-1.0878</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8002</v>
+        <v>-1.5578</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-10.1264</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8008</v>
+        <v>8.5684</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6394</v>
+        <v>-2.1828</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.1715</v>
+        <v>-0.7991999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5321</v>
+        <v>-1.3836</v>
       </c>
       <c r="V2" t="n">
-        <v>1.708</v>
+        <v>4.7578</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3995</v>
+        <v>8.1648</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6915</v>
+        <v>-3.407</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6656</v>
+        <v>5.4235</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5111</v>
+        <v>4.371</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1544</v>
+        <v>1.0527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09799999999999998</v>
+        <v>2.0627</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1156</v>
+        <v>3.5329</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2137</v>
+        <v>-1.4702</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0291</v>
+        <v>6.886099999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2145</v>
+        <v>4.8828</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2436</v>
+        <v>2.0032</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9309999999999999</v>
+        <v>-4.8233</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09889999999999999</v>
+        <v>-1.3499</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0299</v>
+        <v>-3.4734</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6008</v>
+        <v>4.6737</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.3105</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6008</v>
+        <v>7.9842</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3733</v>
+        <v>-1.416</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3775999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004299999999999998</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3401</v>
+        <v>0.1032999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8596999999999999</v>
+        <v>1.4489</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5196</v>
+        <v>-1.3458</v>
       </c>
     </row>
     <row r="4">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6532</v>
+        <v>5.3561</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4963</v>
+        <v>2.6648</v>
       </c>
       <c r="F4" t="n">
-        <v>1.157</v>
+        <v>2.6912</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8972</v>
+        <v>-2.5882</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1245</v>
+        <v>-2.3164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2274</v>
+        <v>-0.2719</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0742</v>
+        <v>0.8008999999999997</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2742</v>
+        <v>-0.3743999999999998</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>1.1753</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8228</v>
+        <v>-3.3891</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8503000000000001</v>
+        <v>-1.942</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02739999999999999</v>
+        <v>-1.447</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4004</v>
+        <v>5.2579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.7789</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4004</v>
+        <v>6.0369</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4905</v>
+        <v>-0.9769</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08880000000000005</v>
+        <v>-1.8588</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5793999999999999</v>
+        <v>0.8817999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6594</v>
+        <v>3.6632</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6594</v>
+        <v>4.5017</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5306</v>
+        <v>3.5872</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5649</v>
+        <v>5.0873</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9657</v>
+        <v>-1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6281</v>
+        <v>-0.1089000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7121</v>
+        <v>-1.2232</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9159</v>
+        <v>1.1144</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6744</v>
+        <v>2.0106</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4707000000000001</v>
+        <v>-0.2589000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2036</v>
+        <v>2.2696</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9537</v>
+        <v>-2.1194</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2413999999999999</v>
+        <v>-0.9643999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7122999999999999</v>
+        <v>-1.155</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4004</v>
+        <v>3.8949</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-1.3631</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4007</v>
+        <v>5.258</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3934</v>
+        <v>4.3546</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6288</v>
+        <v>3.8811</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0222</v>
+        <v>0.4735</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8913</v>
+        <v>-4.5531</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4109</v>
+        <v>-5.1121</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9159</v>
+        <v>0.978</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6158</v>
+        <v>0.7453000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3001</v>
+        <v>0.2325999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2094</v>
+        <v>-0.2789</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2025</v>
+        <v>0.1913</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0069</v>
+        <v>-0.4703000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06</v>
+        <v>0.1632</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1494</v>
+        <v>-0.4421</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1425</v>
+        <v>0.1092</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0069</v>
+        <v>-0.5513000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6262</v>
+        <v>0.7574</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5558</v>
+        <v>0.3028000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0704</v>
+        <v>0.4546</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6802</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6802</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8144</v>
+        <v>0.6531000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3221000000000001</v>
+        <v>-2.2961</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1365</v>
+        <v>2.9492</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2436</v>
+        <v>2.9823</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2997</v>
+        <v>3.5807</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5433</v>
+        <v>-0.5983000000000003</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3976000000000002</v>
+        <v>1.0266</v>
       </c>
       <c r="K7" t="n">
-        <v>0.587</v>
+        <v>3.4331</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9846000000000001</v>
+        <v>-2.4066</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8459999999999999</v>
+        <v>1.9558</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7125</v>
+        <v>0.1476</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5587</v>
+        <v>1.8082</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002000000000001</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0006</v>
+        <v>-4.8685</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6007</v>
+        <v>4.0894</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5494</v>
+        <v>1.1715</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8762000000000001</v>
+        <v>1.2664</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6733</v>
+        <v>-0.09489999999999998</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.09159999999999999</v>
+        <v>-2.7217</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2914</v>
+        <v>-3.0012</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.603</v>
+        <v>-1.5544</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6891999999999999</v>
+        <v>-4.5244</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2921</v>
+        <v>2.97</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7999</v>
+        <v>1.1161</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1541000000000001</v>
+        <v>-1.2243</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.954</v>
+        <v>2.3404</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7193</v>
+        <v>0.09059999999999979</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.131</v>
+        <v>-1.2389</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5884</v>
+        <v>1.3296</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08069999999999999</v>
+        <v>1.0255</v>
       </c>
       <c r="N8" t="n">
-        <v>0.285</v>
+        <v>0.01460000000000003</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3657</v>
+        <v>1.0107</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0006</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.0895</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0006</v>
+        <v>3.3105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7171000000000001</v>
+        <v>-0.2131</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2891</v>
+        <v>-1.364</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5720000000000001</v>
+        <v>1.1511</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1195</v>
+        <v>-1.6785</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3192</v>
+        <v>0.8385</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>-2.517</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4478</v>
+        <v>-1.7455</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8722</v>
+        <v>-8.123900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4245</v>
+        <v>6.378399999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7772</v>
+        <v>-5.1048</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5803</v>
+        <v>-4.6649</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1969</v>
+        <v>-0.4399</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2326</v>
+        <v>-2.8499</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0725</v>
+        <v>-3.7505</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8399</v>
+        <v>0.9005000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5446</v>
+        <v>-2.2546</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5079</v>
+        <v>-0.9142</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0368</v>
+        <v>-1.3404</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4004</v>
+        <v>-1.9475</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-10.321</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4004</v>
+        <v>8.3736</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3644</v>
+        <v>1.4155</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5852</v>
+        <v>0.3694000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7792</v>
+        <v>1.0463</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5399</v>
+        <v>3.891</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5196</v>
+        <v>4.6778</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0595</v>
+        <v>-0.7869</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.484</v>
+        <v>-2.1934</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0865</v>
+        <v>-4.6839</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6026</v>
+        <v>2.4904</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1715</v>
+        <v>0.5330999999999998</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6195</v>
+        <v>4.8868</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.791</v>
+        <v>-4.3536</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6908000000000001</v>
+        <v>6.610099999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2632</v>
+        <v>6.2351</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.954</v>
+        <v>0.375</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5193</v>
+        <v>-6.077</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3563000000000001</v>
+        <v>-1.3484</v>
       </c>
       <c r="O10" t="n">
-        <v>0.163</v>
+        <v>-4.7286</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2000999999999999</v>
+        <v>-5.6474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0006</v>
+        <v>-14.4106</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2007</v>
+        <v>8.763200000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6272</v>
+        <v>-2.7787</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3451</v>
+        <v>-3.5994</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2821</v>
+        <v>0.8206</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1398</v>
+        <v>5.6995</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2598</v>
+        <v>6.7158</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3996</v>
+        <v>-1.0165</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0222</v>
+        <v>-4.7569</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3722</v>
+        <v>-6.2181</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3499</v>
+        <v>1.4612</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.27</v>
+        <v>-7.736499999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.0174</v>
+        <v>-6.4109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2525000000000001</v>
+        <v>-1.3257</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.9387</v>
+        <v>-6.605700000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.3807</v>
+        <v>-6.354699999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.2508000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6687</v>
+        <v>-1.1308</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3632</v>
+        <v>-0.05640000000000006</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3054999999999999</v>
+        <v>-1.0746</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4001</v>
+        <v>1.7526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-5.4527</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4007</v>
+        <v>7.2054</v>
       </c>
       <c r="S11" t="n">
-        <v>2.0796</v>
+        <v>2.7291</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1075</v>
+        <v>2.6628</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.02790000000000004</v>
+        <v>0.06639999999999997</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7681000000000002</v>
+        <v>-1.5022</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4596</v>
+        <v>3.1774</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6914999999999999</v>
+        <v>-4.6797</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3562</v>
+        <v>-6.337800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9592</v>
+        <v>-10.6034</v>
       </c>
       <c r="F12" t="n">
-        <v>2.603</v>
+        <v>4.265400000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1494</v>
+        <v>-11.3334</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2445</v>
+        <v>1.4113</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3938</v>
+        <v>-12.7449</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7813</v>
+        <v>-7.3052</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3251</v>
+        <v>2.4586</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1064</v>
+        <v>-9.7637</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.368</v>
+        <v>-4.0282</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9194000000000001</v>
+        <v>-1.0471</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2874</v>
+        <v>-2.9812</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0012</v>
+        <v>-7.4001</v>
       </c>
       <c r="R12" t="n">
-        <v>3.601</v>
+        <v>8.7631</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3744</v>
+        <v>4.6488</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4359</v>
+        <v>1.7627</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06160000000000002</v>
+        <v>2.8859</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5678</v>
+        <v>-1.0164</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2592</v>
+        <v>2.339</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6915</v>
+        <v>-3.3554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7171</v>
+        <v>-7.5359</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9844</v>
+        <v>-9.182399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2674</v>
+        <v>1.6464</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.56</v>
+        <v>-3.3382</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4051</v>
+        <v>-0.7629000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1549</v>
+        <v>-2.5751</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1646</v>
+        <v>-4.5912</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9686</v>
+        <v>-0.5001000000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.196</v>
+        <v>-4.0913</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3954</v>
+        <v>1.2532</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4366</v>
+        <v>-0.2629</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04109999999999997</v>
+        <v>1.5162</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8005</v>
+        <v>2.5316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0011</v>
+        <v>-3.1158</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2006</v>
+        <v>5.6475</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.536</v>
+        <v>-5.3536</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-3.7627</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2619</v>
+        <v>-1.5909</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1795</v>
+        <v>-1.3758</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9791</v>
+        <v>2.2875</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>-3.6633</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0037</v>
+        <v>-1.6124</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.209800000000001</v>
+        <v>-28.1353</v>
       </c>
       <c r="F14" t="n">
-        <v>15.2134</v>
+        <v>26.52249999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.8495</v>
+        <v>-18.2982</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1726000000000005</v>
+        <v>-1.8234</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.6766</v>
+        <v>-16.4749</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.3196</v>
+        <v>3.625299999999993</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5529</v>
+        <v>6.595399999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.7668</v>
+        <v>-2.970300000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.5296</v>
+        <v>-21.9227</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3797</v>
+        <v>-8.418899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.909799999999999</v>
+        <v>-13.5042</v>
       </c>
       <c r="P14" t="n">
-        <v>9.002700000000001</v>
+        <v>9.5421</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.005</v>
+        <v>-65.2371</v>
       </c>
       <c r="R14" t="n">
-        <v>26.0075</v>
+        <v>74.77909999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>4.490500000000001</v>
+        <v>2.155799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3198</v>
+        <v>-1.7923</v>
       </c>
       <c r="U14" t="n">
-        <v>5.8106</v>
+        <v>3.9482</v>
       </c>
       <c r="V14" t="n">
-        <v>4.359999999999999</v>
+        <v>4.9876</v>
       </c>
       <c r="W14" t="n">
-        <v>17.4345</v>
+        <v>35.2694</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.0748</v>
+        <v>-30.2823</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UROS DE RIVAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UROS DE RIVAS.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5136</v>
+        <v>8.1876</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6285</v>
+        <v>4.951700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.885</v>
+        <v>3.2361</v>
       </c>
       <c r="G2" t="n">
         <v>5.496499999999999</v>
@@ -610,13 +610,13 @@
         <v>8.5684</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1828</v>
+        <v>-0.5086999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7991999999999999</v>
+        <v>-0.4760999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3836</v>
+        <v>-0.03250000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.7578</v>
@@ -643,13 +643,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4235</v>
+        <v>6.688800000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.371</v>
+        <v>4.8695</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0527</v>
+        <v>1.8193</v>
       </c>
       <c r="G3" t="n">
         <v>2.0627</v>
@@ -688,13 +688,13 @@
         <v>7.9842</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.416</v>
+        <v>-0.1509</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6534</v>
+        <v>-0.155</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7625999999999999</v>
+        <v>0.003999999999999948</v>
       </c>
       <c r="V3" t="n">
         <v>0.1032999999999999</v>
@@ -721,13 +721,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3561</v>
+        <v>6.141999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6648</v>
+        <v>3.561900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6912</v>
+        <v>2.5798</v>
       </c>
       <c r="G4" t="n">
         <v>-2.5882</v>
@@ -766,13 +766,13 @@
         <v>6.0369</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9769</v>
+        <v>-0.1910000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.8588</v>
+        <v>-0.9616000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8817999999999999</v>
+        <v>0.7706</v>
       </c>
       <c r="V4" t="n">
         <v>3.6632</v>
@@ -799,13 +799,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5872</v>
+        <v>1.1921</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0873</v>
+        <v>2.3583</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5</v>
+        <v>-1.1661</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1089000000000001</v>
@@ -844,13 +844,13 @@
         <v>5.258</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3546</v>
+        <v>1.9594</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8811</v>
+        <v>1.1519</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4735</v>
+        <v>0.8076</v>
       </c>
       <c r="V5" t="n">
         <v>-4.5531</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.978</v>
+        <v>1.1083</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7453000000000001</v>
+        <v>-1.731499999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2325999999999999</v>
+        <v>2.8397</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2789</v>
+        <v>0.5330999999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1913</v>
+        <v>4.8868</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4703000000000001</v>
+        <v>-4.3536</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1632</v>
+        <v>6.610099999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08210000000000001</v>
+        <v>6.2351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.081</v>
+        <v>0.375</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4421</v>
+        <v>-6.077</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1092</v>
+        <v>-1.3484</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5513000000000001</v>
+        <v>-4.7286</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7789</v>
+        <v>-5.6474</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-14.4106</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>8.763200000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7574</v>
+        <v>0.5229999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3028000000000001</v>
+        <v>-0.6469</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4546</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2795</v>
+        <v>5.6995</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2795</v>
+        <v>6.7158</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.0165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6531000000000001</v>
+        <v>0.5676000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2961</v>
+        <v>0.4463</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9492</v>
+        <v>0.1212</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9823</v>
+        <v>-0.2789</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5807</v>
+        <v>0.1913</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5983000000000003</v>
+        <v>-0.4703000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0266</v>
+        <v>0.1632</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4331</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.4066</v>
+        <v>0.081</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9558</v>
+        <v>-0.4421</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1476</v>
+        <v>0.1092</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8082</v>
+        <v>-0.5513000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7789999999999999</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8685</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.0894</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1715</v>
+        <v>0.3471</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2664</v>
+        <v>0.003700000000000009</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09489999999999998</v>
+        <v>0.3433</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7217</v>
+        <v>-0.2795</v>
       </c>
       <c r="W7" t="n">
         <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.0012</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5544</v>
+        <v>0.1439999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5244</v>
+        <v>-2.9937</v>
       </c>
       <c r="F8" t="n">
-        <v>2.97</v>
+        <v>3.1378</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1161</v>
+        <v>2.9823</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2243</v>
+        <v>3.5807</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3404</v>
+        <v>-0.5983000000000003</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09059999999999979</v>
+        <v>1.0266</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2389</v>
+        <v>3.4331</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3296</v>
+        <v>-2.4066</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0255</v>
+        <v>1.9558</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01460000000000003</v>
+        <v>0.1476</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0107</v>
+        <v>1.8082</v>
       </c>
       <c r="P8" t="n">
         <v>-0.7789999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0895</v>
+        <v>-4.8685</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3105</v>
+        <v>4.0894</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2131</v>
+        <v>0.6622999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.364</v>
+        <v>0.5687</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1511</v>
+        <v>0.09369999999999998</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6785</v>
+        <v>-2.7217</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8385</v>
+        <v>0.2795</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.517</v>
+        <v>-3.0012</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7455</v>
+        <v>-0.7355000000000005</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.123900000000001</v>
+        <v>-3.6033</v>
       </c>
       <c r="F9" t="n">
-        <v>6.378399999999999</v>
+        <v>2.8678</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.1048</v>
+        <v>1.1161</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.6649</v>
+        <v>-1.2243</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4399</v>
+        <v>2.3404</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8499</v>
+        <v>0.09059999999999979</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.7505</v>
+        <v>-1.2389</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9005000000000001</v>
+        <v>1.3296</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2546</v>
+        <v>1.0255</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9142</v>
+        <v>0.01460000000000003</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3404</v>
+        <v>1.0107</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9475</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.321</v>
+        <v>-4.0895</v>
       </c>
       <c r="R9" t="n">
-        <v>8.3736</v>
+        <v>3.3105</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4155</v>
+        <v>0.6059</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3694000000000001</v>
+        <v>-0.4430000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0463</v>
+        <v>1.0489</v>
       </c>
       <c r="V9" t="n">
-        <v>3.891</v>
+        <v>-1.6785</v>
       </c>
       <c r="W9" t="n">
-        <v>4.6778</v>
+        <v>0.8385</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7869</v>
+        <v>-2.517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1934</v>
+        <v>-1.3971</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6839</v>
+        <v>-7.8247</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4904</v>
+        <v>6.4279</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5330999999999998</v>
+        <v>-5.1048</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8868</v>
+        <v>-4.6649</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3536</v>
+        <v>-0.4399</v>
       </c>
       <c r="J10" t="n">
-        <v>6.610099999999999</v>
+        <v>-2.8499</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2351</v>
+        <v>-3.7505</v>
       </c>
       <c r="L10" t="n">
-        <v>0.375</v>
+        <v>0.9005000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.077</v>
+        <v>-2.2546</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3484</v>
+        <v>-0.9142</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.7286</v>
+        <v>-1.3404</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.6474</v>
+        <v>-1.9475</v>
       </c>
       <c r="Q10" t="n">
-        <v>-14.4106</v>
+        <v>-10.321</v>
       </c>
       <c r="R10" t="n">
-        <v>8.763200000000001</v>
+        <v>8.3736</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.7787</v>
+        <v>1.7639</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.5994</v>
+        <v>0.6682</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8206</v>
+        <v>1.0957</v>
       </c>
       <c r="V10" t="n">
-        <v>5.6995</v>
+        <v>3.891</v>
       </c>
       <c r="W10" t="n">
-        <v>6.7158</v>
+        <v>4.6778</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0165</v>
+        <v>-0.7869</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7569</v>
+        <v>-4.985900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.2181</v>
+        <v>-7.1271</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4612</v>
+        <v>2.1411</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.736499999999999</v>
+        <v>-3.3382</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.4109</v>
+        <v>-0.7629000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3257</v>
+        <v>-2.5751</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.605700000000001</v>
+        <v>-4.5912</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.354699999999999</v>
+        <v>-0.5001000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2508000000000001</v>
+        <v>-4.0913</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1308</v>
+        <v>1.2532</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.05640000000000006</v>
+        <v>-0.2629</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0746</v>
+        <v>1.5162</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7526</v>
+        <v>2.5316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.4527</v>
+        <v>-3.1158</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2054</v>
+        <v>5.6475</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7291</v>
+        <v>-2.8036</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6628</v>
+        <v>-1.7074</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06639999999999997</v>
+        <v>-1.0962</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5022</v>
+        <v>-1.3758</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1774</v>
+        <v>2.2875</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.6797</v>
+        <v>-3.6633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.337800000000001</v>
+        <v>-6.507099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6034</v>
+        <v>-7.850700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.265400000000001</v>
+        <v>1.3437</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.3334</v>
+        <v>-7.736499999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4113</v>
+        <v>-6.4109</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.7449</v>
+        <v>-1.3257</v>
       </c>
       <c r="J12" t="n">
-        <v>-7.3052</v>
+        <v>-6.605700000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4586</v>
+        <v>-6.354699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.7637</v>
+        <v>-0.2508000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0282</v>
+        <v>-1.1308</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0471</v>
+        <v>-0.05640000000000006</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9812</v>
+        <v>-1.0746</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3632</v>
+        <v>1.7526</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.4001</v>
+        <v>-5.4527</v>
       </c>
       <c r="R12" t="n">
-        <v>8.7631</v>
+        <v>7.2054</v>
       </c>
       <c r="S12" t="n">
-        <v>4.6488</v>
+        <v>0.979</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7627</v>
+        <v>1.03</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8859</v>
+        <v>-0.05109999999999995</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0164</v>
+        <v>-1.5022</v>
       </c>
       <c r="W12" t="n">
-        <v>2.339</v>
+        <v>3.1774</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.3554</v>
+        <v>-4.6797</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5359</v>
+        <v>-9.404999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.182399999999999</v>
+        <v>-12.5729</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6464</v>
+        <v>3.1678</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3382</v>
+        <v>-11.3334</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7629000000000001</v>
+        <v>1.4113</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5751</v>
+        <v>-12.7449</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.5912</v>
+        <v>-7.3052</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5001000000000002</v>
+        <v>2.4586</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0913</v>
+        <v>-9.7637</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2532</v>
+        <v>-4.0282</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2629</v>
+        <v>-1.0471</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5162</v>
+        <v>-2.9812</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5316</v>
+        <v>1.3632</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1158</v>
+        <v>-7.4001</v>
       </c>
       <c r="R13" t="n">
-        <v>5.6475</v>
+        <v>8.7631</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3536</v>
+        <v>1.5816</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7627</v>
+        <v>-0.2066999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5909</v>
+        <v>1.7883</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3758</v>
+        <v>-1.0164</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2875</v>
+        <v>2.339</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.6633</v>
+        <v>-3.3554</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.6124</v>
+        <v>0.9997999999999969</v>
       </c>
       <c r="E14" t="n">
-        <v>-28.1353</v>
+        <v>-27.5162</v>
       </c>
       <c r="F14" t="n">
-        <v>26.52249999999999</v>
+        <v>28.51609999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-18.2982</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8234</v>
+        <v>-1.823399999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-16.4749</v>
@@ -1522,10 +1522,10 @@
         <v>3.625299999999993</v>
       </c>
       <c r="K14" t="n">
-        <v>6.595399999999998</v>
+        <v>6.595399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.970300000000002</v>
+        <v>-2.970300000000003</v>
       </c>
       <c r="M14" t="n">
         <v>-21.9227</v>
@@ -1537,25 +1537,25 @@
         <v>-13.5042</v>
       </c>
       <c r="P14" t="n">
-        <v>9.5421</v>
+        <v>9.542099999999998</v>
       </c>
       <c r="Q14" t="n">
         <v>-65.2371</v>
       </c>
       <c r="R14" t="n">
-        <v>74.77909999999999</v>
+        <v>74.7791</v>
       </c>
       <c r="S14" t="n">
-        <v>2.155799999999999</v>
+        <v>4.768</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7923</v>
+        <v>-1.1742</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9482</v>
+        <v>5.942299999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9876</v>
+        <v>4.987600000000001</v>
       </c>
       <c r="W14" t="n">
         <v>35.2694</v>
